--- a/output/pdf_financials_xlsx/WBE.xlsx
+++ b/output/pdf_financials_xlsx/WBE.xlsx
@@ -7958,22 +7958,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.30981</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.324865</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.324865</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.326944</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.342901</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.349273</v>
       </c>
     </row>
     <row r="125">
@@ -8016,22 +8016,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.30981</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.324865</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.324865</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.326944</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.342901</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.349273</v>
       </c>
     </row>
     <row r="126">
@@ -22636,7 +22636,11 @@
           <t>Interest portion of lease payments</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -22727,7 +22731,11 @@
           <t>Principal portion of lease payments</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -38301,7 +38309,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -39655,7 +39663,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">

--- a/output/pdf_financials_xlsx/WBE.xlsx
+++ b/output/pdf_financials_xlsx/WBE.xlsx
@@ -2276,16 +2276,16 @@
         <v>0.685415</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.277769</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.277011</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.27701</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.27701</v>
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
@@ -6562,22 +6562,22 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.277769</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.277011</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.27701</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.27701</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.277769</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.27701</v>
       </c>
     </row>
     <row r="101">
@@ -21063,7 +21063,11 @@
           <t>- depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -24112,7 +24116,11 @@
           <t>- depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WBE.xlsx
+++ b/output/pdf_financials_xlsx/WBE.xlsx
@@ -4616,43 +4616,43 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.03715</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.040054</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.044959</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.046296</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.043308</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.045151</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.05848</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.057495</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.063474</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.072755</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.151273</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.04344</v>
       </c>
     </row>
     <row r="68">
@@ -4674,43 +4674,43 @@
         <v>0.673948</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.678211</v>
+        <v>0.715361</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.612019</v>
+        <v>0.652073</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1.121388</v>
+        <v>1.166347</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.96152</v>
+        <v>1.007816</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.805986</v>
+        <v>0.849294</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.782449</v>
+        <v>0.824449</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>1.267813</v>
+        <v>1.312964</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>1.274396</v>
+        <v>1.332876</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>1.054368</v>
+        <v>1.111863</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.9066959999999999</v>
+        <v>0.97017</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.856588</v>
+        <v>0.929343</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.726899</v>
+        <v>0.878172</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>1.271398</v>
+        <v>1.314838</v>
       </c>
     </row>
     <row r="69">
@@ -5080,43 +5080,43 @@
         <v>0.554776</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.35366</v>
+        <v>0.31651</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.061173</v>
+        <v>0.021119</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.548374</v>
+        <v>0.5034149999999999</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.517763</v>
+        <v>0.471467</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.714288</v>
+        <v>0.67098</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.714288</v>
+        <v>0.672288</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.714288</v>
+        <v>0.669137</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.922271</v>
+        <v>0.863791</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>1.182034</v>
+        <v>1.124539</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>1.038948</v>
+        <v>0.975474</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.896798</v>
+        <v>0.824043</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.9518450000000001</v>
+        <v>0.800572</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.581613</v>
+        <v>0.538173</v>
       </c>
     </row>
     <row r="76">
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.01756</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.01317</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.1064</v>
       </c>
       <c r="O107" s="3" t="n">
         <v>0</v>
@@ -25060,7 +25060,11 @@
           <t>- stock option expense</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -29087,7 +29091,11 @@
           <t>- stock option expense</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -33315,7 +33323,11 @@
           <t>- future income tax expense</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -33414,7 +33426,11 @@
           <t>- stock option expense</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="n">
         <v>0.01756</v>
       </c>
@@ -40861,7 +40877,11 @@
           <t>Income tax (recovery) expense 8</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
